--- a/results/nl_summary_statistics.xlsx
+++ b/results/nl_summary_statistics.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>max_rev</t>
+          <t>upper_bound</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
